--- a/artfynd/A 2221-2026 artfynd.xlsx
+++ b/artfynd/A 2221-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546773</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546760</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546762</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546793</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546772</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123309333</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546759</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546783</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546804</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546791</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546799</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1899,6 +1959,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546788</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2000,6 +2065,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546789</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546648</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546797</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2303,6 +2383,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546794</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,6 +2489,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546800</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2505,6 +2595,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546801</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2621,6 +2716,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123309167</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2722,6 +2822,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546792</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2823,6 +2928,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546795</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2924,6 +3034,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546787</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3025,6 +3140,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546798</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3126,6 +3246,11 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546802</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3227,8 +3352,40 @@
           <t>JMN0135 Sälen Idre</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121546805</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>